--- a/Worrobah_Ex3A_tables.xlsx
+++ b/Worrobah_Ex3A_tables.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jordan's River\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C466211-2EC5-4206-A6F8-3A854C6A7A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54BACAA-9740-4B00-B163-67289CDEC333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5F57CCB-800C-4438-989A-A836F1667FC6}"/>
+    <workbookView xWindow="-24120" yWindow="-4440" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{D5F57CCB-800C-4438-989A-A836F1667FC6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Clients" sheetId="1" r:id="rId1"/>
+    <sheet name="Dog" sheetId="2" r:id="rId2"/>
+    <sheet name="Walks" sheetId="3" r:id="rId3"/>
+    <sheet name="Payments" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,6 +41,86 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address </t>
+  </si>
+  <si>
+    <t>EmergencyContact</t>
+  </si>
+  <si>
+    <t>ClientID (PK)</t>
+  </si>
+  <si>
+    <t>DogID (PK)</t>
+  </si>
+  <si>
+    <t>DogName</t>
+  </si>
+  <si>
+    <t>Breed</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Temperament</t>
+  </si>
+  <si>
+    <t>ClientID (FK)</t>
+  </si>
+  <si>
+    <t>WalkDate</t>
+  </si>
+  <si>
+    <t>WalkTime</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>DogID (FK)</t>
+  </si>
+  <si>
+    <t>WalkID (PK)</t>
+  </si>
+  <si>
+    <t>PaymentID (PK)</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>PaymentDate</t>
+  </si>
+  <si>
+    <t>PaymentMethod</t>
+  </si>
+  <si>
+    <t>PaymentStatus</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
@@ -49,12 +132,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,8 +164,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,9 +502,145 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8562D6A-33C5-4D62-AAD5-435237E303C8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7812DB45-DB3A-4B15-875E-0F735876DFEF}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="7" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BB78B08-ADEB-4107-97EA-2E94C94B55C0}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3F5221-1405-4F95-BBE1-9ED4E5D73D26}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="7" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>